--- a/output/pdf_financials_xlsx/OMG.xlsx
+++ b/output/pdf_financials_xlsx/OMG.xlsx
@@ -1264,10 +1264,10 @@
         <v>-0.7444</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.117712</v>
+        <v>-0.18984</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.331957</v>
+        <v>-1.331957</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1.034359</v>
@@ -1276,16 +1276,16 @@
         <v>0.626003</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.587822</v>
+        <v>-0.587822</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.339132</v>
+        <v>-0.339132</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.523157</v>
+        <v>-0.523157</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.393646</v>
+        <v>-0.393646</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-0.355016</v>
@@ -1294,16 +1294,16 @@
         <v>-1.471127</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>7.629568</v>
+        <v>-7.629568</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>7.24834</v>
+        <v>-7.24834</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4.878477</v>
+        <v>-4.878477</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>3.41007</v>
+        <v>-3.41007</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>-5.771841</v>
@@ -1328,10 +1328,10 @@
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.068718</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.252006</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1564,28 +1564,28 @@
         <v>-0.3722</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.036064</v>
+        <v>-0.036064</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.331957</v>
+        <v>-1.331957</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.034359</v>
+        <v>-1.034359</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.626003</v>
+        <v>-0.626003</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.587822</v>
+        <v>-0.587822</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.339132</v>
+        <v>-0.339132</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.523157</v>
+        <v>-0.523157</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.393646</v>
+        <v>-0.393646</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-0.355016</v>
@@ -1594,16 +1594,16 @@
         <v>-1.471127</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>7.629568</v>
+        <v>-7.629568</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>7.24834</v>
+        <v>-7.24834</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>4.878477</v>
+        <v>-4.878477</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>3.41007</v>
+        <v>-3.41007</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>-5.771841</v>
@@ -1738,28 +1738,28 @@
         <v>-0.3722</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.036064</v>
+        <v>-0.036064</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.331957</v>
+        <v>-1.331957</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.034359</v>
+        <v>-1.034359</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.626003</v>
+        <v>-0.626003</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.587822</v>
+        <v>-0.587822</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.339132</v>
+        <v>-0.339132</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.523157</v>
+        <v>-0.523157</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.393646</v>
+        <v>-0.393646</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-0.355016</v>
@@ -1768,16 +1768,16 @@
         <v>-1.471127</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>7.629568</v>
+        <v>-7.629568</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>7.24834</v>
+        <v>-7.24834</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>4.878477</v>
+        <v>-4.878477</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3.41007</v>
+        <v>-3.41007</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>-5.771841</v>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>12.1087</v>
+        <v>-12.1087</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>34.478633</v>
+        <v>-34.478633</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-241.611333</v>
+        <v>241.611333</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-243.92385</v>
+        <v>243.92385</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -2000,10 +2000,10 @@
         <v>-0.7444</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.117712</v>
+        <v>-0.18984</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.331957</v>
+        <v>-1.331957</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>1.034359</v>
@@ -2012,16 +2012,16 @@
         <v>0.626003</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.587822</v>
+        <v>-0.587822</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.339132</v>
+        <v>-0.339132</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.523157</v>
+        <v>-0.523157</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.393646</v>
+        <v>-0.393646</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.355016</v>
@@ -2030,16 +2030,16 @@
         <v>-1.471127</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>7.629568</v>
+        <v>-7.629568</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>7.24834</v>
+        <v>-7.24834</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>4.878477</v>
+        <v>-4.878477</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>3.41007</v>
+        <v>-3.41007</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-5.771841</v>
@@ -2116,10 +2116,10 @@
         <v>-0.7444</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.117712</v>
+        <v>-0.18984</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.331957</v>
+        <v>-1.331957</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>1.034359</v>
@@ -2128,16 +2128,16 @@
         <v>0.626003</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.588381</v>
+        <v>-0.587263</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.339692</v>
+        <v>-0.338572</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.525464</v>
+        <v>-0.52085</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.393646</v>
+        <v>-0.393646</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.355016</v>
@@ -2146,16 +2146,16 @@
         <v>-1.471127</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>7.629568</v>
+        <v>-7.629568</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>7.24834</v>
+        <v>-7.24834</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.878477</v>
+        <v>-4.878477</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>3.41007</v>
+        <v>-3.41007</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-5.771841</v>
@@ -2266,28 +2266,28 @@
         <v>-50</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-130.6374881065652</v>
+        <v>-81.00294985250738</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -2296,16 +2296,16 @@
         <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>-0</v>
@@ -5920,31 +5920,31 @@
         <v>0.069577</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.843206</v>
+        <v>0.8297870000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.837018</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.30293</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.679602</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.217416</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.358128</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.384015</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.208015</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.025887</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>0</v>
@@ -5959,10 +5959,10 @@
         <v>0</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.566114</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.137361</v>
       </c>
     </row>
     <row r="93">
@@ -9857,7 +9857,11 @@
           <t>Warrant reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -18327,7 +18331,11 @@
           <t>Reserves for warrants (note 12)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -19135,7 +19143,11 @@
           <t>Reserves for warrants (note 11)</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -20188,7 +20200,11 @@
           <t>Reserves for warrants (note 12)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -21596,7 +21612,11 @@
           <t>Reserves for warrants (note 10)</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -22396,7 +22416,11 @@
           <t>Reserves for warrants (note 10)</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -44743,16 +44767,16 @@
         </is>
       </c>
       <c r="Q360" s="5" t="n">
-        <v>7.24834</v>
+        <v>-7.24834</v>
       </c>
       <c r="R360" s="5" t="n">
-        <v>4.878477</v>
+        <v>-4.878477</v>
       </c>
       <c r="S360" s="5" t="n">
-        <v>3.41007</v>
+        <v>-3.41007</v>
       </c>
       <c r="T360" s="5" t="n">
-        <v>5.771841</v>
+        <v>-5.771841</v>
       </c>
       <c r="U360" t="inlineStr">
         <is>
@@ -44951,10 +44975,10 @@
         </is>
       </c>
       <c r="S362" s="5" t="n">
-        <v>3.392775</v>
+        <v>-3.392775</v>
       </c>
       <c r="T362" s="5" t="n">
-        <v>5.620378</v>
+        <v>-5.620378</v>
       </c>
       <c r="U362" t="inlineStr">
         <is>
@@ -47035,10 +47059,10 @@
         </is>
       </c>
       <c r="P383" s="5" t="n">
-        <v>7.629568</v>
+        <v>-7.629568</v>
       </c>
       <c r="Q383" s="5" t="n">
-        <v>7.24834</v>
+        <v>-7.24834</v>
       </c>
       <c r="R383" t="inlineStr">
         <is>
@@ -49813,13 +49837,13 @@
         <v>0.626003</v>
       </c>
       <c r="J411" s="5" t="n">
-        <v>0.587822</v>
+        <v>-0.587822</v>
       </c>
       <c r="K411" s="5" t="n">
-        <v>0.339132</v>
+        <v>-0.339132</v>
       </c>
       <c r="L411" s="5" t="n">
-        <v>0.523157</v>
+        <v>-0.523157</v>
       </c>
       <c r="M411" s="5" t="n">
         <v>0.393646</v>
@@ -50411,10 +50435,10 @@
         </is>
       </c>
       <c r="L417" s="5" t="n">
-        <v>0.523157</v>
+        <v>-0.523157</v>
       </c>
       <c r="M417" s="5" t="n">
-        <v>0.393646</v>
+        <v>-0.393646</v>
       </c>
       <c r="N417" t="inlineStr">
         <is>
@@ -51989,16 +52013,16 @@
         </is>
       </c>
       <c r="F433" s="5" t="n">
-        <v>0.036064</v>
+        <v>-0.036064</v>
       </c>
       <c r="G433" s="5" t="n">
-        <v>1.331957</v>
+        <v>-1.331957</v>
       </c>
       <c r="H433" s="5" t="n">
-        <v>1.034359</v>
+        <v>-1.034359</v>
       </c>
       <c r="I433" s="5" t="n">
-        <v>0.626003</v>
+        <v>-0.626003</v>
       </c>
       <c r="J433" t="inlineStr">
         <is>
@@ -52798,10 +52822,10 @@
         </is>
       </c>
       <c r="G441" s="5" t="n">
-        <v>1.331957</v>
+        <v>-1.331957</v>
       </c>
       <c r="H441" s="5" t="n">
-        <v>1.034359</v>
+        <v>-1.034359</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OMG.xlsx
+++ b/output/pdf_financials_xlsx/OMG.xlsx
@@ -1047,13 +1047,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000419</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000118</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-2.9e-05</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1071,13 +1071,13 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.033747</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.119716</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.6536419999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2015,13 +2015,13 @@
         <v>-0.587822</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.339132</v>
+        <v>-0.338713</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.523157</v>
+        <v>-0.523039</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.393646</v>
+        <v>-0.393617</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.355016</v>
@@ -2039,13 +2039,13 @@
         <v>-4.878477</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.41007</v>
+        <v>-3.376323</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-5.771841</v>
+        <v>-5.652125</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-13.587789</v>
+        <v>-12.934147</v>
       </c>
     </row>
     <row r="28">
@@ -2131,13 +2131,13 @@
         <v>-0.587263</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.338572</v>
+        <v>-0.338153</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.52085</v>
+        <v>-0.520732</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.393646</v>
+        <v>-0.393617</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.355016</v>
@@ -2155,13 +2155,13 @@
         <v>-4.878477</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.41007</v>
+        <v>-3.376323</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-5.771841</v>
+        <v>-5.652125</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-13.587789</v>
+        <v>-12.934147</v>
       </c>
     </row>
     <row r="30">
@@ -2465,10 +2465,10 @@
         <v>0.476373</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>6.522853</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>11.725932</v>
       </c>
     </row>
     <row r="35">
@@ -2581,10 +2581,10 @@
         <v>0.476373</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>6.522853</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>30.902533</v>
+        <v>42.628465</v>
       </c>
     </row>
     <row r="37">
@@ -3277,10 +3277,10 @@
         <v>2.905915</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>7.015637</v>
+        <v>0.492784</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>12.484285</v>
+        <v>0.7583530000000001</v>
       </c>
     </row>
     <row r="49">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -43107,7 +43107,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -44606,7 +44606,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">

--- a/output/pdf_financials_xlsx/OMG.xlsx
+++ b/output/pdf_financials_xlsx/OMG.xlsx
@@ -4389,28 +4389,28 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0387</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.680343</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.04032</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.166551</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.18735</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.20693</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.422493</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.218509</v>
       </c>
       <c r="M67" s="3" t="n">
         <v>0.979616</v>
@@ -6967,13 +6967,13 @@
         </is>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.446243</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.349835</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.229654</v>
       </c>
       <c r="O110" s="3" t="n">
         <v>0</v>
@@ -7030,22 +7030,22 @@
         <v>0</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.130878</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.188109</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.093031</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.224163</v>
       </c>
     </row>
     <row r="112">
@@ -8446,22 +8446,22 @@
         <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.130878</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.188109</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.093031</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.224163</v>
       </c>
     </row>
     <row r="135">
@@ -8508,22 +8508,22 @@
         <v>-0.394867</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-4.927437</v>
+        <v>-4.947437</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-6.210509</v>
+        <v>-6.341387</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-4.115239</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-2.336426</v>
+        <v>-2.524535</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-4.521358</v>
+        <v>-4.614389</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-10.676634</v>
+        <v>-10.900797</v>
       </c>
     </row>
   </sheetData>
@@ -26490,7 +26490,11 @@
           <t>Purchase of equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -30229,7 +30233,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -31934,7 +31942,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -32237,7 +32249,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -33053,7 +33069,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -34562,7 +34582,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
